--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H18" authorId="0" shapeId="0">
+    <comment ref="H20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0">
+    <comment ref="L20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="140">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -469,9 +469,6 @@
     <t>WATER_BASED</t>
   </si>
   <si>
-    <t>CLASSIC_COFFEE</t>
-  </si>
-  <si>
     <t>BASIC</t>
   </si>
   <si>
@@ -499,12 +496,6 @@
     <t>nume nu este null</t>
   </si>
   <si>
-    <t>1, 3, 5, 7, 9</t>
-  </si>
-  <si>
-    <t>1, 4, 5, 7, 9</t>
-  </si>
-  <si>
     <t>pret &lt;=0</t>
   </si>
   <si>
@@ -535,9 +526,6 @@
     <t>PLANT_BASED</t>
   </si>
   <si>
-    <t>1, 3, 5, 7, 10</t>
-  </si>
-  <si>
     <t>BUBBLE_TEA</t>
   </si>
   <si>
@@ -556,18 +544,12 @@
     <t>Error message: Invalid price!</t>
   </si>
   <si>
-    <t>2, 3, 5, 7, 9</t>
-  </si>
-  <si>
     <t>preț &gt; 0</t>
   </si>
   <si>
     <t>nume nu este null sau gol</t>
   </si>
   <si>
-    <t>01. preț = -1.0 (invalid, sub limită)</t>
-  </si>
-  <si>
     <t>03. preț - 0.0 (invalid, exact la limită)</t>
   </si>
   <si>
@@ -578,9 +560,6 @@
   </si>
   <si>
     <t>05. preț = 0.02 (valid, imediat peste prima)</t>
-  </si>
-  <si>
-    <t>06. preț = 9999.99 (valid, valoare mare, dar acceptată)</t>
   </si>
   <si>
     <t>07.  nume = null (invalid, referință lipsă)</t>
@@ -635,21 +614,12 @@
     <t>TC8_BVA</t>
   </si>
   <si>
-    <t>TC9_BVA</t>
-  </si>
-  <si>
-    <t>TC10_BVA</t>
-  </si>
-  <si>
     <t>"Matcha"</t>
   </si>
   <si>
     <t>"Ceai Verde"</t>
   </si>
   <si>
-    <t>"Latte Grande"</t>
-  </si>
-  <si>
     <t>"AB"</t>
   </si>
   <si>
@@ -662,9 +632,6 @@
     <t>Error message: Name cannot be empty</t>
   </si>
   <si>
-    <t>"Espresso"</t>
-  </si>
-  <si>
     <t>Error message: Empty name</t>
   </si>
   <si>
@@ -672,6 +639,27 @@
   </si>
   <si>
     <t>passed</t>
+  </si>
+  <si>
+    <t>nume nu este gol</t>
+  </si>
+  <si>
+    <t>nume !=""</t>
+  </si>
+  <si>
+    <t>nume == null</t>
+  </si>
+  <si>
+    <t>1, 5, 7, 9, 11</t>
+  </si>
+  <si>
+    <t>1, 6, 7, 9, 11</t>
+  </si>
+  <si>
+    <t>4, 5, 7, 9, 11</t>
+  </si>
+  <si>
+    <t>1, 5, 7, 9, 12</t>
   </si>
 </sst>
 </file>
@@ -880,7 +868,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1119,7 +1107,70 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="double">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1128,7 +1179,87 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1136,194 +1267,21 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1353,9 +1311,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1366,15 +1321,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1401,17 +1347,53 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1427,254 +1409,211 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2000,24 +1939,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="43"/>
-      <c r="H1" s="34" t="s">
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="51"/>
+      <c r="H1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
@@ -2051,7 +1990,7 @@
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="22"/>
+      <c r="B6" s="18"/>
       <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
@@ -2064,7 +2003,7 @@
     </row>
     <row r="7" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="28" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2125,7 +2064,7 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="28" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2135,7 +2074,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="26" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2179,25 +2118,25 @@
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
-      <c r="B24" s="40" t="s">
+      <c r="A24" s="27"/>
+      <c r="B24" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C26" s="33"/>
+      <c r="C26" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2223,7 +2162,7 @@
     <col min="5" max="5" width="24.5546875" customWidth="1"/>
     <col min="6" max="6" width="5.88671875" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
     <col min="9" max="9" width="4.5546875" customWidth="1"/>
     <col min="10" max="10" width="14.21875" customWidth="1"/>
     <col min="11" max="11" width="17.33203125" customWidth="1"/>
@@ -2236,43 +2175,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
+      <c r="B3" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="60"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="G5" s="106" t="s">
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="G5" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="107"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="107"/>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="108"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="64"/>
     </row>
     <row r="6" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
@@ -2287,39 +2226,39 @@
       <c r="E6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="60" t="s">
+      <c r="G6" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="45" t="s">
+      <c r="I6" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="45" t="s">
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="47"/>
+      <c r="Q6" s="70"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="36" t="s">
-        <v>91</v>
+      <c r="C7" s="56" t="s">
+        <v>90</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="50"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="68"/>
       <c r="I7" s="12" t="s">
         <v>75</v>
       </c>
@@ -2332,187 +2271,187 @@
       <c r="L7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M7" s="45" t="s">
+      <c r="M7" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="N7" s="46"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="45" t="s">
+      <c r="N7" s="71"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="Q7" s="47"/>
+      <c r="Q7" s="70"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>4</v>
       </c>
-      <c r="C8" s="36"/>
+      <c r="C8" s="57"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="38">
+        <v>135</v>
+      </c>
+      <c r="G8" s="32">
         <v>1</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="21">
+      <c r="H8" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="I8" s="17">
         <v>15</v>
       </c>
-      <c r="J8" s="39">
+      <c r="J8" s="33">
         <v>10</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="L8" s="21" t="s">
+      <c r="L8" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="M8" s="62" t="s">
+      <c r="M8" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="N8" s="102"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="62" t="s">
+      <c r="N8" s="72"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="Q8" s="63"/>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>5</v>
       </c>
-      <c r="C9" s="52" t="s">
-        <v>95</v>
+      <c r="C9" s="55" t="s">
+        <v>133</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="38">
+      <c r="G9" s="32">
         <v>2</v>
       </c>
-      <c r="H9" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="I9" s="21">
+      <c r="H9" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="I9" s="17">
         <v>16</v>
       </c>
-      <c r="J9" s="39">
+      <c r="J9" s="33">
         <v>15</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="K9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="M9" s="62" t="s">
+      <c r="L9" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="N9" s="72"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="102"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q9" s="63"/>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>6</v>
       </c>
-      <c r="C10" s="52"/>
+      <c r="C10" s="55"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="38">
+        <v>74</v>
+      </c>
+      <c r="G10" s="32">
         <v>3</v>
       </c>
-      <c r="H10" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="21">
+      <c r="H10" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="I10" s="17">
         <v>17</v>
       </c>
-      <c r="J10" s="39">
+      <c r="J10" s="33">
         <v>18.5</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="L10" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="M10" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="N10" s="102"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q10" s="63"/>
+      <c r="K10" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="M10" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="N10" s="72"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q10" s="54"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>7</v>
       </c>
-      <c r="C11" s="53" t="s">
-        <v>99</v>
+      <c r="C11" s="56" t="s">
+        <v>92</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="38">
+      <c r="G11" s="32">
         <v>4</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="17">
+        <v>18</v>
+      </c>
+      <c r="J11" s="33">
+        <v>-5</v>
+      </c>
+      <c r="K11" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="21">
-        <v>18</v>
-      </c>
-      <c r="J11" s="39">
-        <v>-5</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="M11" s="62" t="s">
+      <c r="L11" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="M11" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="N11" s="72"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="N11" s="102"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q11" s="63"/>
+      <c r="Q11" s="54"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="54"/>
+      <c r="C12" s="57"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>9</v>
       </c>
-      <c r="C13" s="52" t="s">
-        <v>73</v>
+      <c r="C13" s="55" t="s">
+        <v>96</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -2520,28 +2459,49 @@
       <c r="B14" s="4">
         <v>10</v>
       </c>
-      <c r="C14" s="52"/>
+      <c r="C14" s="55"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>94</v>
-      </c>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B15" s="34">
+        <v>11</v>
+      </c>
+      <c r="C15" s="106" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="34"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="D16" t="s">
+      <c r="B16" s="34">
+        <v>12</v>
+      </c>
+      <c r="C16" s="107"/>
+      <c r="D16" s="34" t="s">
         <v>37</v>
       </c>
+      <c r="E16" s="34" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="20" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C11:C12"/>
+  <mergeCells count="24">
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B5:E5"/>
@@ -2553,12 +2513,12 @@
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="M11:O11"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C11:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2570,7 +2530,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:Q17"/>
+  <dimension ref="B1:Q15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -2591,43 +2551,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="57"/>
+      <c r="B3" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="60"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="59"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="64"/>
     </row>
     <row r="6" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
@@ -2640,185 +2600,189 @@
         <v>38</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="G6" s="60" t="s">
+      <c r="G6" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="60" t="s">
+      <c r="H6" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="60" t="s">
+      <c r="I6" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="49" t="s">
+      <c r="J6" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="64" t="s">
+      <c r="K6" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="64" t="s">
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="Q6" s="67"/>
+      <c r="Q6" s="79"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="53">
+      <c r="B7" s="56">
         <v>1</v>
       </c>
-      <c r="C7" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="101" t="s">
-        <v>114</v>
-      </c>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="103" t="s">
+      <c r="C7" s="75" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="104" t="s">
+      <c r="L7" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="M7" s="103" t="s">
-        <v>124</v>
-      </c>
-      <c r="N7" s="103" t="s">
+      <c r="M7" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="N7" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="O7" s="103" t="s">
+      <c r="O7" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="P7" s="95" t="s">
+      <c r="P7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="63"/>
+      <c r="Q7" s="82"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="68"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="101" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="12">
+      <c r="B8" s="74"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="36">
         <v>1</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K8" s="10">
         <v>19</v>
       </c>
-      <c r="L8" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="M8" s="39">
-        <v>-1</v>
-      </c>
-      <c r="N8" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="O8" s="21" t="s">
+      <c r="L8" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="17">
+        <v>-0.01</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="P8" s="62" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q8" s="63"/>
+      <c r="O8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q8" s="54"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="68"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="101" t="s">
-        <v>115</v>
-      </c>
-      <c r="G9" s="12">
+      <c r="B9" s="74"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="36">
         <v>2</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K9" s="10">
         <v>20</v>
       </c>
-      <c r="L9" s="21" t="s">
+      <c r="L9" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="33">
+        <v>0</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="M9" s="21">
-        <v>-0.01</v>
-      </c>
-      <c r="N9" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="P9" s="62" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q9" s="63"/>
+      <c r="P9" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q9" s="54"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="68"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="101" t="s">
-        <v>117</v>
-      </c>
-      <c r="G10" s="12">
+      <c r="B10" s="74"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="36">
         <v>3</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>55</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K10" s="10">
         <v>21</v>
       </c>
-      <c r="L10" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="M10" s="39">
-        <v>0</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="O10" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="P10" s="62" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q10" s="63"/>
+      <c r="L10" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" s="17">
+        <v>0.01</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="P10" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q10" s="54"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="68"/>
-      <c r="C11" s="70"/>
+      <c r="B11" s="56">
+        <v>2</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>108</v>
+      </c>
       <c r="D11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" s="12">
+        <v>113</v>
+      </c>
+      <c r="G11" s="36">
         <v>4</v>
       </c>
       <c r="H11" s="11" t="s">
@@ -2828,282 +2792,200 @@
         <v>53</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K11" s="10">
         <v>22</v>
       </c>
-      <c r="L11" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="M11" s="21">
-        <v>0.01</v>
-      </c>
-      <c r="N11" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="O11" s="21" t="s">
+      <c r="L11" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="M11" s="17">
+        <v>0.02</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="P11" s="62" t="s">
+      <c r="P11" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="Q11" s="63"/>
+      <c r="Q11" s="54"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="54"/>
-      <c r="C12" s="71"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="55"/>
       <c r="D12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G12" s="12">
+        <v>114</v>
+      </c>
+      <c r="G12" s="40">
         <v>5</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" s="34">
+        <v>23</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" s="31">
+        <v>10</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P12" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q12" s="121"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="74"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="40">
+        <v>6</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="34">
+        <v>24</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="31">
+        <v>12</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" s="120" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q13" s="121"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B14" s="57"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="40">
+        <v>7</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="J12" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K12" s="10">
-        <v>23</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="M12" s="21">
-        <v>0.02</v>
-      </c>
-      <c r="N12" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="O12" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="P12" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q12" s="63"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="53">
-        <v>2</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" s="12">
-        <v>6</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K13" s="10">
-        <v>24</v>
-      </c>
-      <c r="L13" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="M13" s="21">
-        <v>9999.99</v>
-      </c>
-      <c r="N13" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="O13" s="21" t="s">
+      <c r="J14" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="P13" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q13" s="63"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="68"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="105">
-        <v>7</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I14" s="35" t="s">
+      <c r="K14" s="34">
+        <v>25</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" s="35">
-        <v>25</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="M14" s="37">
-        <v>10</v>
+      <c r="M14" s="31">
+        <v>15</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>80</v>
       </c>
       <c r="O14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P14" s="120" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q14" s="121"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="G15" s="40">
+        <v>8</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="34">
+        <v>26</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="M15" s="31">
+        <v>20</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="P14" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q14" s="44"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="68"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G15" s="105">
-        <v>8</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="I15" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K15" s="35">
-        <v>26</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M15" s="37">
-        <v>12</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="P15" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q15" s="44"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="54"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G16" s="105">
-        <v>9</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K16" s="35">
-        <v>27</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="37">
-        <v>15</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="P16" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="P15" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="Q16" s="44"/>
-    </row>
-    <row r="17" spans="7:17" x14ac:dyDescent="0.3">
-      <c r="G17" s="105">
-        <v>10</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K17" s="35">
-        <v>28</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="M17" s="37">
-        <v>20</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="P17" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q17" s="44"/>
+      <c r="Q15" s="121"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="23">
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="K6:O6"/>
     <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="B7:B10"/>
     <mergeCell ref="G5:Q5"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="K6:O6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3115,7 +2997,7 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B1:O21"/>
+  <dimension ref="B1:O23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
@@ -3128,117 +3010,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="43"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
     </row>
     <row r="4" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="98" t="s">
+      <c r="C4" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="78" t="s">
+      <c r="D4" s="83" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="51" t="s">
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="51"/>
-    </row>
-    <row r="5" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="83"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="15" t="s">
+      <c r="M4" s="86"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="108"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I5" s="15" t="s">
+      <c r="H5" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="I5" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="93" t="s">
+      <c r="J5" s="112" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="94"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="113"/>
+      <c r="L5" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="35" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6" s="125" t="s">
+      <c r="C6" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="109">
+      <c r="F6" s="38">
         <v>15</v>
       </c>
-      <c r="G6" s="118" t="s">
+      <c r="G6" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="121">
+      <c r="H6" s="45">
         <v>10</v>
       </c>
-      <c r="I6" s="118" t="s">
+      <c r="I6" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="J6" s="127" t="s">
+      <c r="J6" s="114" t="s">
         <v>81</v>
       </c>
-      <c r="K6" s="128"/>
-      <c r="L6" s="112" t="s">
+      <c r="K6" s="114"/>
+      <c r="L6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="113" t="s">
-        <v>143</v>
+      <c r="M6" s="41" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
@@ -3246,69 +3128,69 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="19" t="s">
-        <v>54</v>
+      <c r="C7" s="117"/>
+      <c r="D7" s="36" t="s">
+        <v>86</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="103">
+      <c r="F7" s="38">
         <v>16</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="122">
+      <c r="H7" s="45">
         <v>12</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="95" t="s">
-        <v>103</v>
-      </c>
-      <c r="K7" s="96"/>
+        <v>83</v>
+      </c>
+      <c r="J7" s="114" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="114"/>
       <c r="L7" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="M7" s="110" t="s">
-        <v>143</v>
+        <v>129</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="8">
-        <f t="shared" ref="B8:B13" si="0">B7+1</f>
+        <f t="shared" ref="B8:B14" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="19" t="s">
+      <c r="C8" s="117"/>
+      <c r="D8" s="36" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="103">
+      <c r="F8" s="38">
         <v>17</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="122">
+        <v>89</v>
+      </c>
+      <c r="H8" s="45">
         <v>18.5</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="95" t="s">
-        <v>106</v>
-      </c>
-      <c r="K8" s="96"/>
+        <v>101</v>
+      </c>
+      <c r="J8" s="114" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" s="114"/>
       <c r="L8" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="M8" s="110" t="s">
-        <v>143</v>
+        <v>129</v>
+      </c>
+      <c r="M8" s="41" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
@@ -3316,34 +3198,34 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="19" t="s">
-        <v>89</v>
+      <c r="C9" s="117"/>
+      <c r="D9" s="36" t="s">
+        <v>88</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="110">
+      <c r="F9" s="41">
         <v>18</v>
       </c>
-      <c r="G9" s="119" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="123">
+      <c r="G9" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="46">
         <v>-5</v>
       </c>
-      <c r="I9" s="119" t="s">
-        <v>109</v>
-      </c>
-      <c r="J9" s="114" t="s">
-        <v>106</v>
+      <c r="I9" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="115" t="s">
+        <v>102</v>
       </c>
       <c r="K9" s="115"/>
-      <c r="L9" s="119" t="s">
-        <v>137</v>
-      </c>
-      <c r="M9" s="110" t="s">
-        <v>143</v>
+      <c r="L9" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
@@ -3351,337 +3233,406 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="19" t="s">
+      <c r="C10" s="117"/>
+      <c r="D10" s="36" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="103">
+        <v>119</v>
+      </c>
+      <c r="F10" s="38">
         <v>19</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H10" s="122">
-        <v>-1</v>
+        <v>99</v>
+      </c>
+      <c r="H10" s="119">
+        <v>-0.01</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J10" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="96"/>
+      <c r="J10" s="114" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="114"/>
       <c r="L10" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="M10" s="110" t="s">
-        <v>143</v>
+        <v>127</v>
+      </c>
+      <c r="M10" s="41" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="8">
-        <f t="shared" si="0"/>
+        <f>B10+1</f>
         <v>6</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="19" t="s">
+      <c r="C11" s="117"/>
+      <c r="D11" s="36" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="103">
-        <v>21</v>
+        <v>120</v>
+      </c>
+      <c r="F11" s="38">
+        <v>20</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" s="122">
+        <v>124</v>
+      </c>
+      <c r="H11" s="45">
         <v>0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="J11" s="95" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="96"/>
+        <v>102</v>
+      </c>
+      <c r="J11" s="114" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="114"/>
       <c r="L11" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="M11" s="110" t="s">
-        <v>143</v>
+        <v>127</v>
+      </c>
+      <c r="M11" s="41" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="8">
+        <v>7</v>
+      </c>
+      <c r="C12" s="117"/>
+      <c r="D12" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="38">
+        <v>21</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="119">
+        <v>0.01</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="82"/>
+      <c r="L12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M12" s="41" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="8">
+        <v>8</v>
+      </c>
+      <c r="C13" s="117"/>
+      <c r="D13" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="38">
+        <v>23</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="45">
+        <v>10</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="114" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="114"/>
+      <c r="L13" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="41" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="117"/>
+      <c r="D14" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="103">
-        <v>26</v>
-      </c>
-      <c r="G12" s="9" t="s">
+      <c r="E14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="41">
+        <v>24</v>
+      </c>
+      <c r="G14" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="122">
+      <c r="H14" s="46">
         <v>12</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="J12" s="95" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="96"/>
-      <c r="L12" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="M12" s="110" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="14">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="20" t="s">
+      <c r="I14" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" s="115" t="s">
+        <v>82</v>
+      </c>
+      <c r="K14" s="115"/>
+      <c r="L14" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="M14" s="41" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="13">
+        <v>10</v>
+      </c>
+      <c r="C15" s="118"/>
+      <c r="D15" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E15" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="42">
+        <v>25</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="H15" s="47">
+        <v>15</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="85"/>
+      <c r="L15" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="42" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="97"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="96" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="99"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="98"/>
+      <c r="L19" s="96" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19" s="99"/>
+      <c r="N19" s="97"/>
+      <c r="O19" s="98"/>
+    </row>
+    <row r="20" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="104" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="100" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="101"/>
+      <c r="J20" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20" s="95" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="M20" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="N20" s="94" t="s">
+        <v>64</v>
+      </c>
+      <c r="O20" s="95" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B21" s="92"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="95"/>
+      <c r="L21" s="105"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="94"/>
+      <c r="O21" s="95"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B22" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="19">
+        <v>10</v>
+      </c>
+      <c r="D22" s="21">
+        <v>10</v>
+      </c>
+      <c r="E22" s="21">
+        <v>0</v>
+      </c>
+      <c r="F22" s="22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="25">
+        <v>0</v>
+      </c>
+      <c r="H22" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="111">
-        <v>27</v>
-      </c>
-      <c r="G13" s="120" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="124">
-        <v>15</v>
-      </c>
-      <c r="I13" s="120" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" s="116" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="117"/>
-      <c r="L13" s="120" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="111" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-    </row>
-    <row r="15" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="5"/>
-    </row>
-    <row r="16" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L16" s="5"/>
-    </row>
-    <row r="17" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="75"/>
-      <c r="J17" s="76"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="75"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="77"/>
-    </row>
-    <row r="18" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="86" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="87" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="72" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="92" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" s="88" t="s">
-        <v>68</v>
-      </c>
-      <c r="I18" s="89"/>
-      <c r="J18" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="K18" s="72" t="s">
-        <v>65</v>
-      </c>
-      <c r="L18" s="78" t="s">
-        <v>68</v>
-      </c>
-      <c r="M18" s="73" t="s">
-        <v>63</v>
-      </c>
-      <c r="N18" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="O18" s="72" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="86"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="73"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="73"/>
-      <c r="N19" s="73"/>
-      <c r="O19" s="72"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="23">
-        <v>8</v>
-      </c>
-      <c r="D20" s="25">
-        <v>8</v>
-      </c>
-      <c r="E20" s="25">
+      <c r="I22" s="91"/>
+      <c r="J22" s="21">
         <v>0</v>
       </c>
-      <c r="F20" s="26">
+      <c r="K22" s="22">
         <v>0</v>
       </c>
-      <c r="G20" s="29">
+      <c r="L22" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="M22" s="2">
         <v>0</v>
       </c>
-      <c r="H20" s="84" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="85"/>
-      <c r="J20" s="25">
+      <c r="N22" s="21">
         <v>0</v>
       </c>
-      <c r="K20" s="26">
+      <c r="O22" s="22">
         <v>0</v>
       </c>
-      <c r="L20" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="M20" s="2">
-        <v>0</v>
-      </c>
-      <c r="N20" s="25">
-        <v>0</v>
-      </c>
-      <c r="O20" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="L21" s="3"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L23" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="C6:C13"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
+  <mergeCells count="38">
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:I21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K20:K21"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="F4:K4"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="B3:M3"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C6:C15"/>
     <mergeCell ref="J15:K15"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="H18:I19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="N18:N19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="J12:K12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3690,9 +3641,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3834,19 +3788,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3870,9 +3820,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H20" authorId="0" shapeId="0">
+    <comment ref="H22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0">
+    <comment ref="L22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="140">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -100,9 +100,6 @@
     <t>Lab02. Black-box Testing. ECP, BVA</t>
   </si>
   <si>
-    <t>Echipa</t>
-  </si>
-  <si>
     <t>Numele si prenumele</t>
   </si>
   <si>
@@ -130,10 +127,406 @@
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
   <si>
-    <t>1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
+    <t>Observații</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
+  </si>
+  <si>
+    <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
+  </si>
+  <si>
+    <t>3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora. Condiţiile (constrângerile) rezultă din specificaţii.</t>
+  </si>
+  <si>
+    <t>4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
+  </si>
+  <si>
+    <t>EC Identification</t>
+  </si>
+  <si>
+    <t>EC-based TCs</t>
+  </si>
+  <si>
+    <t>No. EC</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
+    <t>Valid EC</t>
+  </si>
+  <si>
+    <t>Non-valid EC</t>
+  </si>
+  <si>
+    <t>No. TCxx_EC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>input data</t>
+  </si>
+  <si>
+    <t>output data</t>
+  </si>
+  <si>
+    <t>categorie</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
+    <t>record added</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>BVA Condition</t>
+  </si>
+  <si>
+    <t>BVA Condition-based TCs</t>
+  </si>
+  <si>
+    <t>Crt. No.</t>
+  </si>
+  <si>
+    <t>No TCxx_BVA</t>
+  </si>
+  <si>
+    <t>BVA condition</t>
+  </si>
+  <si>
+    <t>Correlated TC</t>
+  </si>
+  <si>
+    <t>Executable</t>
+  </si>
+  <si>
+    <t>expected result</t>
+  </si>
+  <si>
+    <t>BBT TCs</t>
+  </si>
+  <si>
+    <t>Final        TC No.</t>
+  </si>
+  <si>
+    <t>Req. ID</t>
+  </si>
+  <si>
+    <t>ECP TCs</t>
+  </si>
+  <si>
+    <t>BVA TCs</t>
+  </si>
+  <si>
+    <t>actual result</t>
+  </si>
+  <si>
+    <t>F01</t>
+  </si>
+  <si>
+    <t>TC1_ECP</t>
+  </si>
+  <si>
+    <t>TC3_ECP</t>
+  </si>
+  <si>
+    <t>TC3_BVA</t>
+  </si>
+  <si>
+    <t>TC4_BVA</t>
+  </si>
+  <si>
+    <t>TC5_BVA</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Debugging</t>
+  </si>
+  <si>
+    <t>Re-testing</t>
+  </si>
+  <si>
+    <t>Regression Testing</t>
+  </si>
+  <si>
+    <t>#TCs to be run</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">#TCs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="17"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>passed</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">#TCs    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>failed</t>
+    </r>
+  </si>
+  <si>
+    <t>#Bugs</t>
+  </si>
+  <si>
+    <t>#Fixed Bugs</t>
+  </si>
+  <si>
+    <t>Re-tested</t>
+  </si>
+  <si>
+    <t>Kovacs Maria-Melania</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>Stoica Casandra</t>
+  </si>
+  <si>
+    <t>Ciceo Tania-Flavia</t>
+  </si>
+  <si>
+    <t>pret &gt; 0</t>
+  </si>
+  <si>
+    <t>nume == ""</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>pret</t>
+  </si>
+  <si>
+    <t>nume</t>
+  </si>
+  <si>
+    <t>tip</t>
+  </si>
+  <si>
+    <t>"Limonada"</t>
+  </si>
+  <si>
+    <t>JUICE</t>
+  </si>
+  <si>
+    <t>WATER_BASED</t>
+  </si>
+  <si>
+    <t>BASIC</t>
+  </si>
+  <si>
+    <t>MILK_COFFEE</t>
+  </si>
+  <si>
+    <t>DAIRY</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>TC2_ECP</t>
+  </si>
+  <si>
+    <t>"A"</t>
+  </si>
+  <si>
+    <t>TC4_ECP</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>nume nu este null</t>
+  </si>
+  <si>
+    <t>pret &lt;=0</t>
+  </si>
+  <si>
+    <t>nume este String</t>
+  </si>
+  <si>
+    <t>nume !=null</t>
+  </si>
+  <si>
+    <t>orice String</t>
+  </si>
+  <si>
+    <t>non-String (conceptual)</t>
+  </si>
+  <si>
+    <t>preț este numeric</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>non-numeric (conceptual)</t>
+  </si>
+  <si>
+    <t>"Latte"</t>
+  </si>
+  <si>
+    <t>PLANT_BASED</t>
+  </si>
+  <si>
+    <t>BUBBLE_TEA</t>
+  </si>
+  <si>
+    <t>POWDER</t>
+  </si>
+  <si>
+    <t>Error message: Name cannot be empty!</t>
+  </si>
+  <si>
+    <t>"Matcha Latte"</t>
+  </si>
+  <si>
+    <t>TEA</t>
+  </si>
+  <si>
+    <t>Error message: Invalid price!</t>
+  </si>
+  <si>
+    <t>preț &gt; 0</t>
+  </si>
+  <si>
+    <t>nume nu este null sau gol</t>
+  </si>
+  <si>
+    <t>03. preț - 0.0 (invalid, exact la limită)</t>
+  </si>
+  <si>
+    <t>02. preț = -0.01 (invalid, foarte puțin sub limită)</t>
+  </si>
+  <si>
+    <t>04. preț = 0.01 (valid, prima valoare acceptată)</t>
+  </si>
+  <si>
+    <t>05. preț = 0.02 (valid, imediat peste prima)</t>
+  </si>
+  <si>
+    <t>07.  nume = null (invalid, referință lipsă)</t>
+  </si>
+  <si>
+    <t>08. nume = "" (invalid, lungime = 0)</t>
+  </si>
+  <si>
+    <t>09. nume = "A" (valid, minim logic, lungime = 1)</t>
+  </si>
+  <si>
+    <t>10. nume = "AB" (valid, imediat peste minim)</t>
+  </si>
+  <si>
+    <t>preț</t>
+  </si>
+  <si>
+    <t>TC1_BVA</t>
+  </si>
+  <si>
+    <t>TC2_BVA</t>
+  </si>
+  <si>
+    <t>TC6_BVA</t>
+  </si>
+  <si>
+    <t>TC7_BVA</t>
+  </si>
+  <si>
+    <t>TC8_BVA</t>
+  </si>
+  <si>
+    <t>"Matcha"</t>
+  </si>
+  <si>
+    <t>"Ceai Verde"</t>
+  </si>
+  <si>
+    <t>"AB"</t>
+  </si>
+  <si>
+    <t>Error message: Invalid price</t>
+  </si>
+  <si>
+    <t>Error message: Name cannot be null</t>
+  </si>
+  <si>
+    <t>Error message: Name cannot be empty</t>
+  </si>
+  <si>
+    <t>Error message: Empty name</t>
+  </si>
+  <si>
+    <t>not needed</t>
+  </si>
+  <si>
+    <t>passed</t>
+  </si>
+  <si>
+    <t>nume nu este gol</t>
+  </si>
+  <si>
+    <t>nume !=""</t>
+  </si>
+  <si>
+    <t>nume == null</t>
+  </si>
+  <si>
+    <t>1, 5, 7, 9, 11</t>
+  </si>
+  <si>
+    <t>1, 6, 7, 9, 11</t>
+  </si>
+  <si>
+    <t>4, 5, 7, 9, 11</t>
+  </si>
+  <si>
+    <t>1, 5, 7, 9, 12</t>
+  </si>
+  <si>
+    <t>Data: 31.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echipa </t>
+  </si>
+  <si>
+    <t>1. Gestiunea produselor din mydrinkshop</t>
+  </si>
+  <si>
+    <t>Un utilizator dorește să își dezvolte un program pentru gestionarea produselor/băuturilor din drinkshop.</t>
   </si>
   <si>
     <r>
@@ -154,512 +547,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> adăugarea unui film nou (titlu, regizor, an aparitie, actori, categorie, cuvinte cheie);</t>
+      <t xml:space="preserve"> adăugarea unui produs nou (id, nume, preț, categorie, tip);</t>
     </r>
   </si>
   <si>
-    <t>Observații</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
-  </si>
-  <si>
-    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
-  </si>
-  <si>
-    <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
-  </si>
-  <si>
-    <t>3. Se aleg doi parametri ai metodei testate şi se definesc condiţii asupra acestora. Condiţiile (constrângerile) rezultă din specificaţii.</t>
-  </si>
-  <si>
-    <t>4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Exemplu: Parametrii </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>title</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> şi </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">; Condiţii pentru aceşti parametri de intrare: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>title</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> este un string cu lungimea validă de la 1 la 255 caractere; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> este valid dacă ia valori între 1899 şi 2025.</t>
-    </r>
-  </si>
-  <si>
-    <t>EC Identification</t>
-  </si>
-  <si>
-    <t>EC-based TCs</t>
-  </si>
-  <si>
-    <t>No. EC</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>Valid EC</t>
-  </si>
-  <si>
-    <t>Non-valid EC</t>
-  </si>
-  <si>
-    <t>No. TCxx_EC</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>input data</t>
-  </si>
-  <si>
-    <t>output data</t>
-  </si>
-  <si>
-    <t>categorie</t>
-  </si>
-  <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>record added</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>BVA Condition</t>
-  </si>
-  <si>
-    <t>BVA Condition-based TCs</t>
-  </si>
-  <si>
-    <t>Crt. No.</t>
-  </si>
-  <si>
-    <t>No TCxx_BVA</t>
-  </si>
-  <si>
-    <t>BVA condition</t>
-  </si>
-  <si>
-    <t>Correlated TC</t>
-  </si>
-  <si>
-    <t>Executable</t>
-  </si>
-  <si>
-    <t>expected result</t>
-  </si>
-  <si>
-    <t>BBT TCs</t>
-  </si>
-  <si>
-    <t>Final        TC No.</t>
-  </si>
-  <si>
-    <t>Req. ID</t>
-  </si>
-  <si>
-    <t>ECP TCs</t>
-  </si>
-  <si>
-    <t>BVA TCs</t>
-  </si>
-  <si>
-    <t>actual result</t>
-  </si>
-  <si>
-    <t>F01</t>
-  </si>
-  <si>
-    <t>TC1_ECP</t>
-  </si>
-  <si>
-    <t>TC3_ECP</t>
-  </si>
-  <si>
-    <t>TC3_BVA</t>
-  </si>
-  <si>
-    <t>TC4_BVA</t>
-  </si>
-  <si>
-    <t>TC5_BVA</t>
-  </si>
-  <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Debugging</t>
-  </si>
-  <si>
-    <t>Re-testing</t>
-  </si>
-  <si>
-    <t>Regression Testing</t>
-  </si>
-  <si>
-    <t>#TCs to be run</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#TCs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="17"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>passed</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">#TCs    </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>failed</t>
-    </r>
-  </si>
-  <si>
-    <t>#Bugs</t>
-  </si>
-  <si>
-    <t>#Fixed Bugs</t>
-  </si>
-  <si>
-    <t>Re-tested</t>
-  </si>
-  <si>
-    <t>Kovacs Maria-Melania</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>Stoica Casandra</t>
-  </si>
-  <si>
-    <t>Ciceo Tania-Flavia</t>
-  </si>
-  <si>
-    <t>pret &gt; 0</t>
-  </si>
-  <si>
-    <t>nume == ""</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>pret</t>
-  </si>
-  <si>
-    <t>nume</t>
-  </si>
-  <si>
-    <t>tip</t>
-  </si>
-  <si>
-    <t>"Limonada"</t>
-  </si>
-  <si>
-    <t>JUICE</t>
-  </si>
-  <si>
-    <t>WATER_BASED</t>
-  </si>
-  <si>
-    <t>BASIC</t>
-  </si>
-  <si>
-    <t>MILK_COFFEE</t>
-  </si>
-  <si>
-    <t>DAIRY</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>TC2_ECP</t>
-  </si>
-  <si>
-    <t>"A"</t>
-  </si>
-  <si>
-    <t>TC4_ECP</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>nume nu este null</t>
-  </si>
-  <si>
-    <t>pret &lt;=0</t>
-  </si>
-  <si>
-    <t>nume este String</t>
-  </si>
-  <si>
-    <t>nume !=null</t>
-  </si>
-  <si>
-    <t>orice String</t>
-  </si>
-  <si>
-    <t>non-String (conceptual)</t>
-  </si>
-  <si>
-    <t>preț este numeric</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>non-numeric (conceptual)</t>
-  </si>
-  <si>
-    <t>"Latte"</t>
-  </si>
-  <si>
-    <t>PLANT_BASED</t>
-  </si>
-  <si>
-    <t>BUBBLE_TEA</t>
-  </si>
-  <si>
-    <t>POWDER</t>
-  </si>
-  <si>
-    <t>Error message: Name cannot be empty!</t>
-  </si>
-  <si>
-    <t>"Matcha Latte"</t>
-  </si>
-  <si>
-    <t>TEA</t>
-  </si>
-  <si>
-    <t>Error message: Invalid price!</t>
-  </si>
-  <si>
-    <t>preț &gt; 0</t>
-  </si>
-  <si>
-    <t>nume nu este null sau gol</t>
-  </si>
-  <si>
-    <t>03. preț - 0.0 (invalid, exact la limită)</t>
-  </si>
-  <si>
-    <t>02. preț = -0.01 (invalid, foarte puțin sub limită)</t>
-  </si>
-  <si>
-    <t>04. preț = 0.01 (valid, prima valoare acceptată)</t>
-  </si>
-  <si>
-    <t>05. preț = 0.02 (valid, imediat peste prima)</t>
-  </si>
-  <si>
-    <t>07.  nume = null (invalid, referință lipsă)</t>
-  </si>
-  <si>
-    <t>08. nume = "" (invalid, lungime = 0)</t>
-  </si>
-  <si>
-    <t>09. nume = "A" (valid, minim logic, lungime = 1)</t>
-  </si>
-  <si>
-    <t>10. nume = "AB" (valid, imediat peste minim)</t>
-  </si>
-  <si>
-    <t>preț</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>F01.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> adăugarea unui produs nou (nume, preț, categorie, tip);</t>
-    </r>
-  </si>
-  <si>
-    <t>TC1_BVA</t>
-  </si>
-  <si>
-    <t>TC2_BVA</t>
-  </si>
-  <si>
-    <t>TC6_BVA</t>
-  </si>
-  <si>
-    <t>TC7_BVA</t>
-  </si>
-  <si>
-    <t>TC8_BVA</t>
-  </si>
-  <si>
-    <t>"Matcha"</t>
-  </si>
-  <si>
-    <t>"Ceai Verde"</t>
-  </si>
-  <si>
-    <t>"AB"</t>
-  </si>
-  <si>
-    <t>Error message: Invalid price</t>
-  </si>
-  <si>
-    <t>Error message: Name cannot be null</t>
-  </si>
-  <si>
-    <t>Error message: Name cannot be empty</t>
-  </si>
-  <si>
-    <t>Error message: Empty name</t>
-  </si>
-  <si>
-    <t>not needed</t>
-  </si>
-  <si>
-    <t>passed</t>
-  </si>
-  <si>
-    <t>nume nu este gol</t>
-  </si>
-  <si>
-    <t>nume !=""</t>
-  </si>
-  <si>
-    <t>nume == null</t>
-  </si>
-  <si>
-    <t>1, 5, 7, 9, 11</t>
-  </si>
-  <si>
-    <t>1, 6, 7, 9, 11</t>
-  </si>
-  <si>
-    <t>4, 5, 7, 9, 11</t>
-  </si>
-  <si>
-    <t>1, 5, 7, 9, 12</t>
+    <t>addProduct(int id, String nume, double pret, CategorieBautura categorie, TipBautura tip): void</t>
+  </si>
+  <si>
+    <t>Exemplu: Exemplu: Parametrii nume și pret; Condiții pentru acești parametri de intrare: nume este valid dacă nu este null și nu este gol; pret este valid dacă are valori strict mai mari decât 0.</t>
   </si>
 </sst>
 </file>
@@ -669,7 +564,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,21 +603,6 @@
       <b/>
       <sz val="11"/>
       <color indexed="17"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="30"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color indexed="30"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -823,6 +703,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -868,7 +755,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1277,13 +1164,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1291,42 +1215,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1334,94 +1258,121 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1433,43 +1384,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1484,136 +1447,124 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1938,121 +1889,124 @@
     <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1" s="49" t="s">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="51"/>
-      <c r="H1" s="30" t="s">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+      <c r="H1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H2" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I1" s="29"/>
+      <c r="J1" s="130" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" s="130"/>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H2" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="2" t="s">
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H5" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="18"/>
       <c r="H6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="28" t="s">
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2064,28 +2018,28 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="28" t="s">
-        <v>15</v>
+      <c r="B18" s="27" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C20" s="26" t="s">
-        <v>17</v>
+      <c r="C20" s="25" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2102,7 +2056,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2118,31 +2072,32 @@
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="27"/>
-      <c r="B24" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C26" s="29"/>
+      <c r="C26" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B24:N24"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="J1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2175,283 +2130,283 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="51"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="60"/>
+      <c r="B3" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="G5" s="62" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="64"/>
+      <c r="B5" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="G5" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="73"/>
     </row>
     <row r="6" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="70"/>
+      <c r="Q6" s="64"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="56" t="s">
-        <v>90</v>
+      <c r="C7" s="78" t="s">
+        <v>84</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="68"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="77"/>
       <c r="I7" s="12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="N7" s="71"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="70"/>
+        <v>26</v>
+      </c>
+      <c r="M7" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="N7" s="63"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="64"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>4</v>
       </c>
-      <c r="C8" s="57"/>
+      <c r="C8" s="79"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G8" s="32">
+        <v>128</v>
+      </c>
+      <c r="G8" s="31">
         <v>1</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="I8" s="17">
         <v>15</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="32">
         <v>10</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="M8" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="72"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q8" s="54"/>
+        <v>74</v>
+      </c>
+      <c r="M8" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="N8" s="65"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="61"/>
     </row>
     <row r="9" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>5</v>
       </c>
-      <c r="C9" s="55" t="s">
-        <v>133</v>
+      <c r="C9" s="66" t="s">
+        <v>126</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="G9" s="32">
+      <c r="G9" s="31">
         <v>2</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I9" s="17">
         <v>16</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="32">
         <v>15</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="M9" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="N9" s="72"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q9" s="54"/>
+        <v>77</v>
+      </c>
+      <c r="M9" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="N9" s="65"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9" s="61"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>6</v>
       </c>
-      <c r="C10" s="55"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="32">
+        <v>68</v>
+      </c>
+      <c r="G10" s="31">
         <v>3</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="I10" s="17">
         <v>17</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10" s="32">
         <v>18.5</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="M10" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="N10" s="72"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q10" s="54"/>
+        <v>95</v>
+      </c>
+      <c r="M10" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="65"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q10" s="61"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>7</v>
       </c>
-      <c r="C11" s="56" t="s">
-        <v>92</v>
+      <c r="C11" s="78" t="s">
+        <v>86</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="G11" s="32">
+      <c r="G11" s="31">
         <v>4</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I11" s="17">
         <v>18</v>
       </c>
-      <c r="J11" s="33">
+      <c r="J11" s="32">
         <v>-5</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="M11" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="N11" s="72"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q11" s="54"/>
+        <v>99</v>
+      </c>
+      <c r="M11" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="65"/>
+      <c r="O11" s="61"/>
+      <c r="P11" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="61"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="79"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>9</v>
       </c>
-      <c r="C13" s="55" t="s">
-        <v>96</v>
+      <c r="C13" s="66" t="s">
+        <v>90</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -2459,42 +2414,55 @@
       <c r="B14" s="4">
         <v>10</v>
       </c>
-      <c r="C14" s="55"/>
+      <c r="C14" s="66"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B15" s="34">
+      <c r="B15" s="33">
         <v>11</v>
       </c>
-      <c r="C15" s="106" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="34"/>
+      <c r="C15" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="33"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B16" s="34">
+      <c r="B16" s="33">
         <v>12</v>
       </c>
-      <c r="C16" s="107"/>
-      <c r="D16" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>91</v>
+      <c r="C16" s="58"/>
+      <c r="D16" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:Q5"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="P8:Q8"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="P11:Q11"/>
@@ -2503,22 +2471,9 @@
     <mergeCell ref="M8:O8"/>
     <mergeCell ref="M9:O9"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:Q5"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="P7:Q7"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="M11:O11"/>
-    <mergeCell ref="C7:C8"/>
     <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C11:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2551,429 +2506,418 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="51"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="60"/>
+      <c r="B3" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="77" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
+      <c r="B5" s="90" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="64"/>
+      <c r="G5" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="73"/>
     </row>
     <row r="6" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="G6" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="86"/>
+      <c r="P6" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="G6" s="65" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="65" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="78" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="79"/>
+      <c r="Q6" s="86"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="56">
+      <c r="B7" s="78">
         <v>1</v>
       </c>
-      <c r="C7" s="75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="L7" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="M7" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="N7" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="P7" s="80" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" s="82"/>
+      <c r="C7" s="88" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="L7" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="P7" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" s="83"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="74"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="36">
+      <c r="B8" s="87"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="35">
         <v>1</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K8" s="10">
         <v>19</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="M8" s="17">
         <v>-0.01</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="O8" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="P8" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q8" s="54"/>
+        <v>78</v>
+      </c>
+      <c r="P8" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="61"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="74"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="36">
+      <c r="B9" s="87"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="35">
         <v>2</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K9" s="10">
         <v>20</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="M9" s="33">
+        <v>117</v>
+      </c>
+      <c r="M9" s="32">
         <v>0</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="P9" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q9" s="54"/>
+        <v>96</v>
+      </c>
+      <c r="P9" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q9" s="61"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="74"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G10" s="36">
+      <c r="B10" s="87"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="35">
         <v>3</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K10" s="10">
         <v>21</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M10" s="17">
         <v>0.01</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="P10" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q10" s="54"/>
+        <v>75</v>
+      </c>
+      <c r="P10" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="61"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="56">
+      <c r="B11" s="78">
         <v>2</v>
       </c>
-      <c r="C11" s="55" t="s">
-        <v>108</v>
+      <c r="C11" s="66" t="s">
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G11" s="36">
+        <v>107</v>
+      </c>
+      <c r="G11" s="35">
         <v>4</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K11" s="10">
         <v>22</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="M11" s="17">
         <v>0.02</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O11" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="P11" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="61"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B12" s="87"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="39">
+        <v>5</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" s="33">
+        <v>23</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" s="30">
+        <v>10</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P12" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q12" s="81"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B13" s="87"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="39">
+        <v>6</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="33">
+        <v>24</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" s="30">
+        <v>12</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P13" s="80" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q13" s="81"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B14" s="79"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="39">
+        <v>7</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="33">
+        <v>25</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="P11" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q11" s="54"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="74"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G12" s="40">
-        <v>5</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" s="34">
-        <v>23</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="M12" s="31">
-        <v>10</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12" s="120" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q12" s="121"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="74"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G13" s="40">
-        <v>6</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K13" s="34">
-        <v>24</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M13" s="31">
-        <v>12</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P13" s="120" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q13" s="121"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="57"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="2" t="s">
+      <c r="M14" s="30">
+        <v>15</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q14" s="81"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="G15" s="39">
+        <v>8</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="40">
-        <v>7</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K14" s="34">
-        <v>25</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" s="31">
-        <v>15</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P14" s="120" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q14" s="121"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="G15" s="40">
-        <v>8</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>53</v>
+      <c r="I15" s="33" t="s">
+        <v>47</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K15" s="34">
+        <v>79</v>
+      </c>
+      <c r="K15" s="33">
         <v>26</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M15" s="31">
+        <v>119</v>
+      </c>
+      <c r="M15" s="30">
         <v>20</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="P15" s="120" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q15" s="121"/>
+        <v>94</v>
+      </c>
+      <c r="P15" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q15" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P14:Q14"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -2986,6 +2930,17 @@
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P13:Q13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2997,7 +2952,7 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B1:O23"/>
+  <dimension ref="B1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
@@ -3010,117 +2965,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="51"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="88" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
+      <c r="B3" s="113" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
     </row>
     <row r="4" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="65" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="87" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="67" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="86" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="86"/>
+      <c r="B4" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="97" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="109" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="109"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="108"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="112" t="s">
-        <v>78</v>
-      </c>
-      <c r="K5" s="113"/>
-      <c r="L5" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="35" t="s">
-        <v>51</v>
+      <c r="B5" s="118"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="115" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="116"/>
+      <c r="L5" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6" s="116" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>53</v>
+      <c r="C6" s="120" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>47</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="38">
+        <v>29</v>
+      </c>
+      <c r="F6" s="37">
         <v>15</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="45">
+        <v>73</v>
+      </c>
+      <c r="H6" s="44">
         <v>10</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J6" s="114" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K6" s="114"/>
       <c r="L6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="41" t="s">
-        <v>132</v>
+        <v>28</v>
+      </c>
+      <c r="M6" s="40" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
@@ -3128,69 +3083,69 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="117"/>
-      <c r="D7" s="36" t="s">
-        <v>86</v>
+      <c r="C7" s="121"/>
+      <c r="D7" s="35" t="s">
+        <v>80</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="38">
+        <v>29</v>
+      </c>
+      <c r="F7" s="37">
         <v>16</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="45">
+        <v>30</v>
+      </c>
+      <c r="H7" s="44">
         <v>12</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J7" s="114" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K7" s="114"/>
       <c r="L7" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="M7" s="41" t="s">
-        <v>132</v>
+        <v>122</v>
+      </c>
+      <c r="M7" s="40" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="8">
-        <f t="shared" ref="B8:B14" si="0">B7+1</f>
+        <f t="shared" ref="B8:B15" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="117"/>
-      <c r="D8" s="36" t="s">
-        <v>54</v>
+      <c r="C8" s="121"/>
+      <c r="D8" s="35" t="s">
+        <v>48</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="38">
+        <v>29</v>
+      </c>
+      <c r="F8" s="37">
         <v>17</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="45">
+        <v>83</v>
+      </c>
+      <c r="H8" s="44">
         <v>18.5</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J8" s="114" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="K8" s="114"/>
       <c r="L8" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="M8" s="41" t="s">
-        <v>132</v>
+        <v>122</v>
+      </c>
+      <c r="M8" s="40" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
@@ -3198,34 +3153,34 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="36" t="s">
-        <v>88</v>
+      <c r="C9" s="121"/>
+      <c r="D9" s="35" t="s">
+        <v>82</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="41">
+        <v>29</v>
+      </c>
+      <c r="F9" s="40">
         <v>18</v>
       </c>
-      <c r="G9" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="H9" s="46">
+      <c r="G9" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="45">
         <v>-5</v>
       </c>
-      <c r="I9" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="J9" s="115" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" s="115"/>
-      <c r="L9" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="M9" s="41" t="s">
-        <v>132</v>
+      <c r="I9" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="119"/>
+      <c r="L9" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="M9" s="40" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
@@ -3233,34 +3188,34 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="117"/>
-      <c r="D10" s="36" t="s">
-        <v>35</v>
+      <c r="C10" s="121"/>
+      <c r="D10" s="35" t="s">
+        <v>29</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="38">
+        <v>112</v>
+      </c>
+      <c r="F10" s="37">
         <v>19</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="119">
+        <v>93</v>
+      </c>
+      <c r="H10" s="51">
         <v>-0.01</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J10" s="114" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K10" s="114"/>
       <c r="L10" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="M10" s="41" t="s">
-        <v>132</v>
+        <v>120</v>
+      </c>
+      <c r="M10" s="40" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.3">
@@ -3268,371 +3223,439 @@
         <f>B10+1</f>
         <v>6</v>
       </c>
-      <c r="C11" s="117"/>
-      <c r="D11" s="36" t="s">
-        <v>35</v>
+      <c r="C11" s="121"/>
+      <c r="D11" s="35" t="s">
+        <v>29</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="38">
+        <v>113</v>
+      </c>
+      <c r="F11" s="37">
         <v>20</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="45">
+        <v>117</v>
+      </c>
+      <c r="H11" s="44">
         <v>0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K11" s="114"/>
       <c r="L11" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="M11" s="41" t="s">
-        <v>132</v>
+        <v>120</v>
+      </c>
+      <c r="M11" s="40" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="8">
         <v>7</v>
       </c>
-      <c r="C12" s="117"/>
-      <c r="D12" s="36" t="s">
-        <v>35</v>
-      </c>
+      <c r="C12" s="121"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="38">
+        <v>49</v>
+      </c>
+      <c r="F12" s="49">
         <v>21</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="119">
+        <v>73</v>
+      </c>
+      <c r="H12" s="51">
         <v>0.01</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="80" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" s="82"/>
+        <v>74</v>
+      </c>
+      <c r="J12" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="83"/>
       <c r="L12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" s="41" t="s">
-        <v>132</v>
+        <v>28</v>
+      </c>
+      <c r="M12" s="50" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="8">
         <v>8</v>
       </c>
-      <c r="C13" s="117"/>
-      <c r="D13" s="36" t="s">
-        <v>35</v>
+      <c r="C13" s="121"/>
+      <c r="D13" s="35" t="s">
+        <v>29</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="38">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="F13" s="49">
+        <v>22</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H13" s="45">
-        <v>10</v>
+        <v>118</v>
+      </c>
+      <c r="H13" s="51">
+        <v>0.02</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" s="114" t="s">
-        <v>82</v>
-      </c>
-      <c r="K13" s="114"/>
+        <v>99</v>
+      </c>
+      <c r="J13" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="83"/>
       <c r="L13" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="M13" s="41" t="s">
-        <v>132</v>
+        <v>28</v>
+      </c>
+      <c r="M13" s="50" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="8">
+        <v>9</v>
+      </c>
+      <c r="C14" s="121"/>
+      <c r="D14" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="37">
+        <v>23</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="44">
+        <v>10</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="114" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="114"/>
+      <c r="L14" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="M14" s="40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="8">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C14" s="117"/>
-      <c r="D14" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" s="41">
+        <v>10</v>
+      </c>
+      <c r="C15" s="121"/>
+      <c r="D15" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="40">
         <v>24</v>
       </c>
-      <c r="G14" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="46">
+      <c r="G15" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="45">
         <v>12</v>
       </c>
-      <c r="I14" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="J14" s="115" t="s">
-        <v>82</v>
-      </c>
-      <c r="K14" s="115"/>
-      <c r="L14" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="M14" s="41" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="13">
-        <v>10</v>
-      </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15" s="42">
+      <c r="I15" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="J15" s="119" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="119"/>
+      <c r="L15" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="128">
+        <v>11</v>
+      </c>
+      <c r="C16" s="121"/>
+      <c r="D16" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="41">
         <v>25</v>
       </c>
-      <c r="G15" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="47">
+      <c r="G16" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="46">
         <v>15</v>
       </c>
-      <c r="I15" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" s="84" t="s">
-        <v>82</v>
-      </c>
-      <c r="K15" s="85"/>
-      <c r="L15" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="42" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="15" t="s">
+      <c r="I16" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="123" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="124"/>
+      <c r="L16" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="13">
+        <v>12</v>
+      </c>
+      <c r="C17" s="122"/>
+      <c r="D17" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" s="41">
+        <v>26</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="46">
+        <v>20</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" s="123" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17" s="124"/>
+      <c r="L17" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+    </row>
+    <row r="19" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="93" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="94"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="125" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="126"/>
+      <c r="N21" s="126"/>
+      <c r="O21" s="127"/>
+    </row>
+    <row r="22" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="89"/>
-      <c r="K17" s="89"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L18" s="5"/>
-    </row>
-    <row r="19" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="96" t="s">
+      <c r="E22" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="20" t="s">
+      <c r="F22" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="H19" s="96" t="s">
+      <c r="G22" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="99"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="96" t="s">
+      <c r="H22" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="M19" s="99"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="98"/>
-    </row>
-    <row r="20" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="93" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="94" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="95" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20" s="104" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="100" t="s">
-        <v>68</v>
-      </c>
-      <c r="I20" s="101"/>
-      <c r="J20" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="K20" s="95" t="s">
-        <v>65</v>
-      </c>
-      <c r="L20" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="M20" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="N20" s="94" t="s">
-        <v>64</v>
-      </c>
-      <c r="O20" s="95" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="92"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="95"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="95"/>
-      <c r="L21" s="105"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="94"/>
-      <c r="O21" s="95"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="19">
-        <v>10</v>
-      </c>
-      <c r="D22" s="21">
-        <v>10</v>
-      </c>
-      <c r="E22" s="21">
+      <c r="I22" s="105"/>
+      <c r="J22" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22" s="91" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="O22" s="92" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B23" s="102"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="92"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="19">
+        <v>12</v>
+      </c>
+      <c r="D24" s="21">
+        <v>12</v>
+      </c>
+      <c r="E24" s="21">
         <v>0</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F24" s="22">
         <v>0</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G24" s="129">
         <v>0</v>
       </c>
-      <c r="H22" s="90" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" s="91"/>
-      <c r="J22" s="21">
+      <c r="H24" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" s="101"/>
+      <c r="J24" s="21">
         <v>0</v>
       </c>
-      <c r="K22" s="22">
+      <c r="K24" s="22">
         <v>0</v>
       </c>
-      <c r="L22" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="M22" s="2">
+      <c r="L24" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="M24" s="2">
         <v>0</v>
       </c>
-      <c r="N22" s="21">
+      <c r="N24" s="21">
         <v>0</v>
       </c>
-      <c r="O22" s="22">
+      <c r="O24" s="22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="L23" s="3"/>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L25" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="O20:O21"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="M20:M21"/>
+  <mergeCells count="40">
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C6:C17"/>
     <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:I21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="K20:K21"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="F4:K4"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="B3:M3"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C6:C15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3641,12 +3664,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3788,15 +3808,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3820,10 +3844,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="141">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -555,6 +555,9 @@
   </si>
   <si>
     <t>Exemplu: Exemplu: Parametrii nume și pret; Condiții pentru acești parametri de intrare: nume este valid dacă nu este null și nu este gol; pret este valid dacă are valori strict mai mari decât 0.</t>
+  </si>
+  <si>
+    <t>needed</t>
   </si>
 </sst>
 </file>
@@ -1330,6 +1333,12 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1345,6 +1354,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1354,65 +1423,35 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1420,32 +1459,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1456,35 +1543,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1501,71 +1567,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1890,27 +1893,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="57"/>
       <c r="H1" s="29" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="29"/>
-      <c r="J1" s="130" t="s">
+      <c r="J1" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="K1" s="130"/>
+      <c r="K1" s="59"/>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H2" s="56" t="s">
+      <c r="H2" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H3" s="2"/>
@@ -2073,21 +2076,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="26"/>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="52"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C26" s="28"/>
@@ -2130,43 +2133,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="G5" s="71" t="s">
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="G5" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="73"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="69"/>
     </row>
     <row r="6" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
@@ -2181,39 +2184,39 @@
       <c r="E6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="76" t="s">
+      <c r="H6" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="62" t="s">
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="64"/>
+      <c r="Q6" s="75"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="61" t="s">
         <v>84</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>87</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="77"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="73"/>
       <c r="I7" s="12" t="s">
         <v>69</v>
       </c>
@@ -2226,21 +2229,21 @@
       <c r="L7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="62" t="s">
+      <c r="M7" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="N7" s="63"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="62" t="s">
+      <c r="N7" s="76"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="Q7" s="64"/>
+      <c r="Q7" s="75"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>4</v>
       </c>
-      <c r="C8" s="79"/>
+      <c r="C8" s="62"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>128</v>
@@ -2263,21 +2266,21 @@
       <c r="L8" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="M8" s="60" t="s">
+      <c r="M8" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="N8" s="65"/>
-      <c r="O8" s="61"/>
-      <c r="P8" s="60" t="s">
+      <c r="N8" s="82"/>
+      <c r="O8" s="78"/>
+      <c r="P8" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="Q8" s="61"/>
+      <c r="Q8" s="78"/>
     </row>
     <row r="9" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>5</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="60" t="s">
         <v>126</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -2302,21 +2305,21 @@
       <c r="L9" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="M9" s="60" t="s">
+      <c r="M9" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="N9" s="65"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="60" t="s">
+      <c r="N9" s="82"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="Q9" s="61"/>
+      <c r="Q9" s="78"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>6</v>
       </c>
-      <c r="C10" s="66"/>
+      <c r="C10" s="60"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>68</v>
@@ -2339,21 +2342,21 @@
       <c r="L10" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="M10" s="60" t="s">
+      <c r="M10" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="N10" s="65"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="60" t="s">
+      <c r="N10" s="82"/>
+      <c r="O10" s="78"/>
+      <c r="P10" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="Q10" s="61"/>
+      <c r="Q10" s="78"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>7</v>
       </c>
-      <c r="C11" s="78" t="s">
+      <c r="C11" s="61" t="s">
         <v>86</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -2378,21 +2381,21 @@
       <c r="L11" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="M11" s="60" t="s">
+      <c r="M11" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="N11" s="65"/>
-      <c r="O11" s="61"/>
-      <c r="P11" s="60" t="s">
+      <c r="N11" s="82"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="Q11" s="61"/>
+      <c r="Q11" s="78"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="79"/>
+      <c r="C12" s="62"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>89</v>
@@ -2402,7 +2405,7 @@
       <c r="B13" s="4">
         <v>9</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="60" t="s">
         <v>90</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -2414,7 +2417,7 @@
       <c r="B14" s="4">
         <v>10</v>
       </c>
-      <c r="C14" s="66"/>
+      <c r="C14" s="60"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>92</v>
@@ -2424,7 +2427,7 @@
       <c r="B15" s="33">
         <v>11</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="79" t="s">
         <v>67</v>
       </c>
       <c r="D15" s="33" t="s">
@@ -2436,7 +2439,7 @@
       <c r="B16" s="33">
         <v>12</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="33" t="s">
         <v>31</v>
       </c>
@@ -2445,11 +2448,22 @@
       </c>
     </row>
     <row r="20" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="P9:Q9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="C11:C12"/>
@@ -2463,17 +2477,6 @@
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="P9:Q9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2506,43 +2509,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="73"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="69"/>
     </row>
     <row r="6" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
@@ -2555,44 +2558,44 @@
         <v>32</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="74" t="s">
+      <c r="H6" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="74" t="s">
+      <c r="I6" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="76" t="s">
+      <c r="J6" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="84" t="s">
+      <c r="K6" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="86"/>
-      <c r="P6" s="84" t="s">
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="88"/>
+      <c r="P6" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="Q6" s="86"/>
+      <c r="Q6" s="88"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="78">
+      <c r="B7" s="61">
         <v>1</v>
       </c>
-      <c r="C7" s="88" t="s">
+      <c r="C7" s="84" t="s">
         <v>101</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="77"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="73"/>
       <c r="K7" s="37" t="s">
         <v>69</v>
       </c>
@@ -2608,14 +2611,14 @@
       <c r="O7" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="P7" s="82" t="s">
+      <c r="P7" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="Q7" s="83"/>
+      <c r="Q7" s="90"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="87"/>
-      <c r="C8" s="89"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="36" t="s">
         <v>103</v>
       </c>
@@ -2646,14 +2649,14 @@
       <c r="O8" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="P8" s="60" t="s">
+      <c r="P8" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="Q8" s="61"/>
+      <c r="Q8" s="78"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="87"/>
-      <c r="C9" s="89"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="36" t="s">
         <v>105</v>
       </c>
@@ -2684,14 +2687,14 @@
       <c r="O9" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="P9" s="60" t="s">
+      <c r="P9" s="77" t="s">
         <v>120</v>
       </c>
-      <c r="Q9" s="61"/>
+      <c r="Q9" s="78"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="87"/>
-      <c r="C10" s="89"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="36" t="s">
         <v>106</v>
       </c>
@@ -2722,16 +2725,16 @@
       <c r="O10" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="P10" s="60" t="s">
+      <c r="P10" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="61"/>
+      <c r="Q10" s="78"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="78">
+      <c r="B11" s="61">
         <v>2</v>
       </c>
-      <c r="C11" s="66" t="s">
+      <c r="C11" s="60" t="s">
         <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -2764,14 +2767,14 @@
       <c r="O11" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="P11" s="60" t="s">
+      <c r="P11" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="Q11" s="61"/>
+      <c r="Q11" s="78"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="87"/>
-      <c r="C12" s="66"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="60"/>
       <c r="D12" s="2" t="s">
         <v>108</v>
       </c>
@@ -2802,14 +2805,14 @@
       <c r="O12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="P12" s="80" t="s">
+      <c r="P12" s="92" t="s">
         <v>121</v>
       </c>
-      <c r="Q12" s="81"/>
+      <c r="Q12" s="93"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="87"/>
-      <c r="C13" s="66"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="60"/>
       <c r="D13" s="2" t="s">
         <v>109</v>
       </c>
@@ -2840,14 +2843,14 @@
       <c r="O13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="P13" s="80" t="s">
+      <c r="P13" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="Q13" s="81"/>
+      <c r="Q13" s="93"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="79"/>
-      <c r="C14" s="66"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="60"/>
       <c r="D14" s="2" t="s">
         <v>110</v>
       </c>
@@ -2878,10 +2881,10 @@
       <c r="O14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="P14" s="80" t="s">
+      <c r="P14" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="Q14" s="81"/>
+      <c r="Q14" s="93"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="G15" s="39">
@@ -2911,13 +2914,20 @@
       <c r="O15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="80" t="s">
+      <c r="P15" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="Q15" s="81"/>
+      <c r="Q15" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P13:Q13"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -2934,13 +2944,6 @@
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="K6:O6"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P13:Q13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2965,12 +2968,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="113" t="s">
@@ -2989,35 +2992,35 @@
       <c r="M3" s="113"/>
     </row>
     <row r="4" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="70" t="s">
         <v>41</v>
       </c>
       <c r="C4" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="97" t="s">
+      <c r="D4" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="F4" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="64"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="75"/>
       <c r="L4" s="109" t="s">
         <v>25</v>
       </c>
       <c r="M4" s="109"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="118"/>
+      <c r="B5" s="105"/>
       <c r="C5" s="112"/>
-      <c r="D5" s="117"/>
+      <c r="D5" s="104"/>
       <c r="E5" s="110"/>
       <c r="F5" s="34" t="s">
         <v>69</v>
@@ -3031,10 +3034,10 @@
       <c r="I5" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="115" t="s">
+      <c r="J5" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="102"/>
       <c r="L5" s="34" t="s">
         <v>27</v>
       </c>
@@ -3046,7 +3049,7 @@
       <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6" s="120" t="s">
+      <c r="C6" s="106" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="35" t="s">
@@ -3067,10 +3070,10 @@
       <c r="I6" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="J6" s="114" t="s">
+      <c r="J6" s="99" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="114"/>
+      <c r="K6" s="99"/>
       <c r="L6" s="7" t="s">
         <v>28</v>
       </c>
@@ -3083,7 +3086,7 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="121"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="35" t="s">
         <v>80</v>
       </c>
@@ -3102,10 +3105,10 @@
       <c r="I7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="114" t="s">
+      <c r="J7" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="K7" s="114"/>
+      <c r="K7" s="99"/>
       <c r="L7" s="7" t="s">
         <v>122</v>
       </c>
@@ -3118,7 +3121,7 @@
         <f t="shared" ref="B8:B15" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="121"/>
+      <c r="C8" s="107"/>
       <c r="D8" s="35" t="s">
         <v>48</v>
       </c>
@@ -3137,10 +3140,10 @@
       <c r="I8" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="J8" s="114" t="s">
+      <c r="J8" s="99" t="s">
         <v>96</v>
       </c>
-      <c r="K8" s="114"/>
+      <c r="K8" s="99"/>
       <c r="L8" s="7" t="s">
         <v>122</v>
       </c>
@@ -3153,7 +3156,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="121"/>
+      <c r="C9" s="107"/>
       <c r="D9" s="35" t="s">
         <v>82</v>
       </c>
@@ -3172,10 +3175,10 @@
       <c r="I9" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="J9" s="119" t="s">
+      <c r="J9" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="K9" s="119"/>
+      <c r="K9" s="100"/>
       <c r="L9" s="42" t="s">
         <v>120</v>
       </c>
@@ -3188,7 +3191,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="121"/>
+      <c r="C10" s="107"/>
       <c r="D10" s="35" t="s">
         <v>29</v>
       </c>
@@ -3207,10 +3210,10 @@
       <c r="I10" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="114" t="s">
+      <c r="J10" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="114"/>
+      <c r="K10" s="99"/>
       <c r="L10" s="7" t="s">
         <v>120</v>
       </c>
@@ -3223,7 +3226,7 @@
         <f>B10+1</f>
         <v>6</v>
       </c>
-      <c r="C11" s="121"/>
+      <c r="C11" s="107"/>
       <c r="D11" s="35" t="s">
         <v>29</v>
       </c>
@@ -3242,10 +3245,10 @@
       <c r="I11" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="J11" s="114" t="s">
+      <c r="J11" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="K11" s="114"/>
+      <c r="K11" s="99"/>
       <c r="L11" s="7" t="s">
         <v>120</v>
       </c>
@@ -3257,7 +3260,7 @@
       <c r="B12" s="8">
         <v>7</v>
       </c>
-      <c r="C12" s="121"/>
+      <c r="C12" s="107"/>
       <c r="D12" s="48"/>
       <c r="E12" s="8" t="s">
         <v>49</v>
@@ -3274,10 +3277,10 @@
       <c r="I12" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="J12" s="82" t="s">
+      <c r="J12" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="83"/>
+      <c r="K12" s="90"/>
       <c r="L12" s="7" t="s">
         <v>28</v>
       </c>
@@ -3289,7 +3292,7 @@
       <c r="B13" s="8">
         <v>8</v>
       </c>
-      <c r="C13" s="121"/>
+      <c r="C13" s="107"/>
       <c r="D13" s="35" t="s">
         <v>29</v>
       </c>
@@ -3308,10 +3311,10 @@
       <c r="I13" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="J13" s="82" t="s">
+      <c r="J13" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="K13" s="83"/>
+      <c r="K13" s="90"/>
       <c r="L13" s="7" t="s">
         <v>28</v>
       </c>
@@ -3323,7 +3326,7 @@
       <c r="B14" s="8">
         <v>9</v>
       </c>
-      <c r="C14" s="121"/>
+      <c r="C14" s="107"/>
       <c r="D14" s="35" t="s">
         <v>29</v>
       </c>
@@ -3342,10 +3345,10 @@
       <c r="I14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="114" t="s">
+      <c r="J14" s="99" t="s">
         <v>76</v>
       </c>
-      <c r="K14" s="114"/>
+      <c r="K14" s="99"/>
       <c r="L14" s="7" t="s">
         <v>121</v>
       </c>
@@ -3358,7 +3361,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C15" s="121"/>
+      <c r="C15" s="107"/>
       <c r="D15" s="35" t="s">
         <v>29</v>
       </c>
@@ -3377,10 +3380,10 @@
       <c r="I15" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="J15" s="119" t="s">
+      <c r="J15" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="K15" s="119"/>
+      <c r="K15" s="100"/>
       <c r="L15" s="42" t="s">
         <v>123</v>
       </c>
@@ -3389,10 +3392,10 @@
       </c>
     </row>
     <row r="16" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="128">
+      <c r="B16" s="52">
         <v>11</v>
       </c>
-      <c r="C16" s="121"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="47" t="s">
         <v>29</v>
       </c>
@@ -3411,10 +3414,10 @@
       <c r="I16" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="123" t="s">
+      <c r="J16" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="K16" s="124"/>
+      <c r="K16" s="98"/>
       <c r="L16" s="43" t="s">
         <v>28</v>
       </c>
@@ -3426,7 +3429,7 @@
       <c r="B17" s="13">
         <v>12</v>
       </c>
-      <c r="C17" s="122"/>
+      <c r="C17" s="108"/>
       <c r="D17" s="14" t="s">
         <v>29</v>
       </c>
@@ -3445,10 +3448,10 @@
       <c r="I17" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="123" t="s">
+      <c r="J17" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="K17" s="124"/>
+      <c r="K17" s="98"/>
       <c r="L17" s="43" t="s">
         <v>28</v>
       </c>
@@ -3481,93 +3484,93 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="99"/>
-      <c r="K19" s="99"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="114"/>
       <c r="L19" s="5"/>
     </row>
     <row r="20" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L20" s="5"/>
     </row>
     <row r="21" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="93" t="s">
+      <c r="C21" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="96"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="123"/>
       <c r="G21" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="H21" s="93" t="s">
+      <c r="H21" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="I21" s="94"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="125" t="s">
+      <c r="I21" s="124"/>
+      <c r="J21" s="122"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="M21" s="126"/>
-      <c r="N21" s="126"/>
-      <c r="O21" s="127"/>
+      <c r="M21" s="95"/>
+      <c r="N21" s="95"/>
+      <c r="O21" s="96"/>
     </row>
     <row r="22" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="103" t="s">
+      <c r="C22" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="91" t="s">
+      <c r="D22" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="91" t="s">
+      <c r="E22" s="119" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="92" t="s">
+      <c r="F22" s="120" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="108" t="s">
+      <c r="G22" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="H22" s="104" t="s">
+      <c r="H22" s="125" t="s">
         <v>62</v>
       </c>
-      <c r="I22" s="105"/>
-      <c r="J22" s="91" t="s">
+      <c r="I22" s="126"/>
+      <c r="J22" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="K22" s="92" t="s">
+      <c r="K22" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="L22" s="97" t="s">
+      <c r="L22" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="M22" s="91" t="s">
+      <c r="M22" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="N22" s="91" t="s">
+      <c r="N22" s="119" t="s">
         <v>58</v>
       </c>
-      <c r="O22" s="92" t="s">
+      <c r="O22" s="120" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23" s="102"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="107"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="92"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="120"/>
+      <c r="L23" s="130"/>
+      <c r="M23" s="119"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="120"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="23" t="s">
@@ -3577,23 +3580,23 @@
         <v>12</v>
       </c>
       <c r="D24" s="21">
+        <v>4</v>
+      </c>
+      <c r="E24" s="21">
+        <v>8</v>
+      </c>
+      <c r="F24" s="22">
+        <v>8</v>
+      </c>
+      <c r="G24" s="53">
+        <v>8</v>
+      </c>
+      <c r="H24" s="115" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="116"/>
+      <c r="J24" s="21">
         <v>12</v>
-      </c>
-      <c r="E24" s="21">
-        <v>0</v>
-      </c>
-      <c r="F24" s="22">
-        <v>0</v>
-      </c>
-      <c r="G24" s="129">
-        <v>0</v>
-      </c>
-      <c r="H24" s="100" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="101"/>
-      <c r="J24" s="21">
-        <v>0</v>
       </c>
       <c r="K24" s="22">
         <v>0</v>
@@ -3616,6 +3619,35 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="H22:I23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="F4:K4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C6:C17"/>
+    <mergeCell ref="J17:K17"/>
     <mergeCell ref="L21:O21"/>
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="J8:K8"/>
@@ -3626,36 +3658,7 @@
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C6:C17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="F4:K4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B3:M3"/>
     <mergeCell ref="J19:K19"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="H22:I23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="O22:O23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="M22:M23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3664,9 +3667,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3808,19 +3814,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3844,9 +3846,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>